--- a/cerdanyola_excelencia_400_700k.xlsx
+++ b/cerdanyola_excelencia_400_700k.xlsx
@@ -2725,7 +2725,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>luminoso · tranquilo</t>
+          <t>exterior · luminoso · tranquilo</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>tranquilo</t>
+          <t>exterior · vistas · tranquilo</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4087,29 +4087,29 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>0.124</v>
+        <v>0.274</v>
       </c>
       <c r="Y30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
-        <v>420000</v>
+        <v>415000</v>
       </c>
       <c r="AA30" t="n">
+        <v>425000</v>
+      </c>
+      <c r="AB30" t="n">
         <v>430000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>435000</v>
       </c>
       <c r="AC30" t="n">
         <v>435000</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>act fast (well-priced; open &lt;5% below)</t>
+          <t>standard (open ~5-8% below)</t>
         </is>
       </c>
       <c r="AE30" t="n">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>✓ base 3% — descuento mediano que acaban aceptando los anuncios que se retiran del mercado; ✗ días online: solo 0 días (percentil 0%) — anuncio aún fresco, sin palanca (+0); ✗ bajadas de precio: ninguna observada todavía (+0); ✗ multi-agencia: solo lo vemos en una fuente (+0); ✗ relistado: no detectado (+0); ✗ reactivaciones: ninguna (+0); ✗ texto motivado: sin señales tipo herencia/urge/negociable (+0); ✗ sobreprecio: ya pide un 19% por DEBAJO de su valor de mercado — buen precio, poco recorrido extra (+0); ✓ el mercado en tu banda se está enfriando (buyer score alto) (+1%)</t>
+          <t>✓ base 3% — descuento mediano que acaban aceptando los anuncios que se retiran del mercado; ✗ días online: solo 0 días (percentil 0%) — anuncio aún fresco, sin palanca (+0); ✗ bajadas de precio: ninguna observada todavía (+0); ✗ multi-agencia: solo lo vemos en una fuente (+0); ✗ relistado: no detectado (+0); ✗ reactivaciones: ninguna (+0); ✓ el texto del anuncio sugiere vendedor motivado (renovation) (+2%); ✗ sobreprecio: ya pide un 19% por DEBAJO de su valor de mercado — buen precio, poco recorrido extra (+0); ✓ el mercado en tu banda se está enfriando (buyer score alto) (+1%)</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
